--- a/templates/chaekmu_template.xlsx
+++ b/templates/chaekmu_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uesr\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\workspace\chaekmu-parser\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F1B620-7D66-44AA-9211-46E7FE38F5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110EB3A5-6063-403C-AE56-778AB233BEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C2CA835E-0E26-42BF-B47A-02E4DF383C87}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="189">
   <si>
     <t>임원별 책무기술서</t>
   </si>
@@ -65,12 +65,6 @@
   </si>
   <si>
     <t>책무 배분일자</t>
-  </si>
-  <si>
-    <t>책무명</t>
-  </si>
-  <si>
-    <t>세부 관리의무</t>
   </si>
   <si>
     <t>§1. 임원 및 직책 정보</t>
@@ -619,6 +613,10 @@
     <t>회의체 0개면 1행 남기고 N/A 표시
 행 조정은 반드시 뒤에서 앞으로 (관리의무→책무→회의체)
 ※ 행 삭제 후 데이터 범위 밖 잔존 셀 정리 필수 (9번 참조)</t>
+  </si>
+  <si>
+    <t>관리의무</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1836,8 +1834,8 @@
   <autoFilter ref="A36:C46" xr:uid="{F5D5E6B5-ACB3-44F7-8B78-849C8D552418}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{55BA41CB-16FA-4ED1-A23A-15B2BB1AA6EA}" name="구분" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{4955E0BA-8CE2-4642-AD5F-03ED5361BFDE}" name="책무명" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{59F1D040-406C-4CA8-BDEA-C0C094B8A904}" name="세부 관리의무" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{4955E0BA-8CE2-4642-AD5F-03ED5361BFDE}" name="책무 세부내용" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{59F1D040-406C-4CA8-BDEA-C0C094B8A904}" name="관리의무" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2171,7 +2169,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A1" s="57" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="56"/>
@@ -2179,7 +2177,7 @@
     </row>
     <row r="2" spans="1:4" ht="27" x14ac:dyDescent="0.3">
       <c r="A2" s="58" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56"/>
@@ -2193,7 +2191,7 @@
     </row>
     <row r="4" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" s="67"/>
       <c r="C4" s="67"/>
@@ -2201,7 +2199,7 @@
     </row>
     <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="56"/>
@@ -2209,7 +2207,7 @@
     </row>
     <row r="6" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A6" s="56" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" s="56"/>
       <c r="C6" s="56"/>
@@ -2217,7 +2215,7 @@
     </row>
     <row r="7" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A7" s="59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="56"/>
       <c r="C7" s="56"/>
@@ -2231,7 +2229,7 @@
     </row>
     <row r="9" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" s="67" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="67"/>
       <c r="C9" s="67"/>
@@ -2239,73 +2237,73 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="60" t="s">
         <v>42</v>
-      </c>
-      <c r="B10" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>44</v>
       </c>
       <c r="D10" s="56"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="56" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>47</v>
       </c>
       <c r="D11" s="56"/>
     </row>
     <row r="12" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="56" t="s">
         <v>48</v>
-      </c>
-      <c r="B12" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>50</v>
       </c>
       <c r="D12" s="56"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="56" t="s">
         <v>51</v>
-      </c>
-      <c r="B13" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="56" t="s">
-        <v>53</v>
       </c>
       <c r="D13" s="56"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="56" t="s">
         <v>54</v>
-      </c>
-      <c r="B14" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="56" t="s">
-        <v>56</v>
       </c>
       <c r="D14" s="56"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="56" t="s">
         <v>57</v>
-      </c>
-      <c r="B15" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="56" t="s">
-        <v>59</v>
       </c>
       <c r="D15" s="56"/>
     </row>
@@ -2317,7 +2315,7 @@
     </row>
     <row r="17" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="67" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="67"/>
@@ -2325,128 +2323,128 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="D18" s="60" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" s="60" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A19" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="D19" s="56" t="s">
         <v>66</v>
-      </c>
-      <c r="C19" s="56" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="56" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A20" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="D20" s="56" t="s">
         <v>70</v>
-      </c>
-      <c r="C20" s="56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="56" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="56" t="s">
+      <c r="D21" s="56" t="s">
         <v>74</v>
-      </c>
-      <c r="C21" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="56" t="s">
-        <v>79</v>
-      </c>
       <c r="D22" s="61" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="56" t="s">
         <v>80</v>
-      </c>
-      <c r="B23" s="56" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="D23" s="56" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="56" t="s">
         <v>83</v>
-      </c>
-      <c r="B24" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="56" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="56" t="s">
         <v>88</v>
-      </c>
-      <c r="B26" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="56" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2457,7 +2455,7 @@
     </row>
     <row r="28" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="67" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B28" s="67"/>
       <c r="C28" s="67"/>
@@ -2465,22 +2463,22 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="60" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B29" s="60" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D29" s="56"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="56" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C30" s="56" t="s">
         <v>1</v>
@@ -2489,10 +2487,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="56" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" s="56" t="s">
         <v>2</v>
@@ -2501,10 +2499,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="56" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" s="56" t="s">
         <v>3</v>
@@ -2513,34 +2511,34 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D33" s="56"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="56" t="s">
         <v>102</v>
-      </c>
-      <c r="B34" s="56" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>104</v>
       </c>
       <c r="D34" s="56"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="56" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C35" s="56" t="s">
         <v>5</v>
@@ -2549,10 +2547,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="56" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36" s="56" t="s">
         <v>6</v>
@@ -2561,34 +2559,34 @@
     </row>
     <row r="37" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A37" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="56" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="56" t="s">
         <v>109</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="56" t="s">
-        <v>111</v>
       </c>
       <c r="D37" s="56"/>
     </row>
     <row r="38" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A38" s="56" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C38" s="61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D38" s="56"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="56" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C39" s="56" t="s">
         <v>12</v>
@@ -2597,25 +2595,25 @@
     </row>
     <row r="40" spans="1:4" ht="132" x14ac:dyDescent="0.3">
       <c r="A40" s="56" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B40" s="56" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C40" s="61" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" s="56"/>
     </row>
     <row r="41" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A41" s="56" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C41" s="56" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D41" s="56"/>
     </row>
@@ -2627,7 +2625,7 @@
     </row>
     <row r="43" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A43" s="67" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B43" s="67"/>
       <c r="C43" s="67"/>
@@ -2635,53 +2633,53 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="60" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B44" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="60" t="s">
         <v>121</v>
-      </c>
-      <c r="C44" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="60" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A45" s="56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B45" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="56" t="s">
-        <v>125</v>
-      </c>
-      <c r="C45" s="56" t="s">
-        <v>126</v>
-      </c>
       <c r="D45" s="56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="56" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B46" s="56" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C46" s="56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D46" s="56"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B47" s="56" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C47" s="56" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D47" s="56"/>
     </row>
@@ -2693,7 +2691,7 @@
     </row>
     <row r="49" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A49" s="67" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B49" s="67"/>
       <c r="C49" s="67"/>
@@ -2701,49 +2699,49 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="60" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B50" s="60" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D50" s="56"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B51" s="56" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C51" s="56" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D51" s="56"/>
     </row>
     <row r="52" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A52" s="56" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B52" s="56" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C52" s="56" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D52" s="56"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="B53" s="56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" s="56" t="s">
         <v>136</v>
-      </c>
-      <c r="B53" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="56" t="s">
-        <v>138</v>
       </c>
       <c r="D53" s="56"/>
     </row>
@@ -2755,7 +2753,7 @@
     </row>
     <row r="55" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A55" s="67" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B55" s="67"/>
       <c r="C55" s="67"/>
@@ -2763,40 +2761,40 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="60" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B56" s="60" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C56" s="56"/>
       <c r="D56" s="56"/>
     </row>
     <row r="57" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A57" s="56" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B57" s="56" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C57" s="56"/>
       <c r="D57" s="56"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="56" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C58" s="56"/>
       <c r="D58" s="56"/>
     </row>
     <row r="59" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A59" s="56" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B59" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C59" s="56"/>
       <c r="D59" s="56"/>
@@ -2809,7 +2807,7 @@
     </row>
     <row r="61" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A61" s="67" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B61" s="67"/>
       <c r="C61" s="67"/>
@@ -2817,47 +2815,47 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="60" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B62" s="60" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C62" s="56"/>
       <c r="D62" s="56"/>
     </row>
     <row r="63" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A63" s="56" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B63" s="56" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C63" s="56"/>
       <c r="D63" s="56"/>
     </row>
     <row r="64" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A64" s="56" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B64" s="56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C64" s="56"/>
       <c r="D64" s="56"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="56" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C65" s="56"/>
       <c r="D65" s="56"/>
     </row>
     <row r="67" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A67" s="62" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B67" s="63"/>
       <c r="C67" s="63"/>
@@ -2865,51 +2863,51 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C68" s="65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>161</v>
+      </c>
+      <c r="B69" t="s">
+        <v>162</v>
+      </c>
+      <c r="C69" t="s">
         <v>163</v>
-      </c>
-      <c r="B69" t="s">
-        <v>164</v>
-      </c>
-      <c r="C69" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70" s="56" t="s">
         <v>166</v>
-      </c>
-      <c r="B70" t="s">
-        <v>167</v>
-      </c>
-      <c r="C70" s="56" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>167</v>
+      </c>
+      <c r="B71" t="s">
+        <v>168</v>
+      </c>
+      <c r="C71" t="s">
         <v>169</v>
-      </c>
-      <c r="B71" t="s">
-        <v>170</v>
-      </c>
-      <c r="C71" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A73" s="66" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B73" s="63"/>
       <c r="C73" s="63"/>
@@ -2917,57 +2915,57 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="65" t="s">
         <v>172</v>
-      </c>
-      <c r="B74" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="C74" s="65" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" t="s">
         <v>175</v>
-      </c>
-      <c r="B75" t="s">
-        <v>176</v>
-      </c>
-      <c r="C75" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" t="s">
         <v>178</v>
-      </c>
-      <c r="B76" t="s">
-        <v>179</v>
-      </c>
-      <c r="C76" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>179</v>
+      </c>
+      <c r="B77" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" t="s">
         <v>181</v>
-      </c>
-      <c r="B77" t="s">
-        <v>182</v>
-      </c>
-      <c r="C77" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" t="s">
         <v>184</v>
-      </c>
-      <c r="B78" t="s">
-        <v>185</v>
-      </c>
-      <c r="C78" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3005,12 +3003,12 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3050,7 +3048,7 @@
     </row>
     <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="44"/>
       <c r="C8" s="45"/>
@@ -3088,7 +3086,7 @@
     </row>
     <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="47"/>
       <c r="C13" s="47"/>
@@ -3134,17 +3132,17 @@
     </row>
     <row r="19" spans="1:6" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="35" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="38"/>
     </row>
     <row r="20" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="33"/>
@@ -3182,7 +3180,7 @@
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
@@ -3190,13 +3188,13 @@
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="D26" s="54"/>
     </row>
@@ -3232,17 +3230,17 @@
     </row>
     <row r="32" spans="1:6" ht="80.099999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" s="41"/>
       <c r="D32" s="38"/>
     </row>
     <row r="33" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="32" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33" s="33"/>
       <c r="C33" s="33"/>
@@ -3258,7 +3256,7 @@
     </row>
     <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B35" s="47"/>
       <c r="C35" s="47"/>
@@ -3266,13 +3264,13 @@
     </row>
     <row r="36" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="D36" s="54"/>
     </row>
@@ -3332,10 +3330,10 @@
     </row>
     <row r="46" spans="1:6" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="35" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B46" s="36" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C46" s="37"/>
       <c r="D46" s="23"/>
